--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104062</v>
+        <v>104065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104062</v>
+        <v>104065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 31070-2026 artfynd.xlsx
+++ b/artfynd/A 31070-2026 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>136046753</v>
       </c>
       <c r="B4" t="n">
-        <v>104065</v>
+        <v>104066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>136055735</v>
       </c>
       <c r="B5" t="n">
-        <v>104065</v>
+        <v>104066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>136046924</v>
       </c>
       <c r="B10" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136047204</v>
       </c>
       <c r="B11" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136049371</v>
       </c>
       <c r="B12" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>136056088</v>
       </c>
       <c r="B13" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
